--- a/data/compare/pending-do-vs-ls-launch.xlsx
+++ b/data/compare/pending-do-vs-ls-launch.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId2"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5032" uniqueCount="2377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5055" uniqueCount="2381">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -6935,6 +6935,9 @@
     <t xml:space="preserve">8 Key Kalimba</t>
   </si>
   <si>
+    <t xml:space="preserve">ADD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curved Diamond Groove Copper Bottle</t>
   </si>
   <si>
@@ -7013,6 +7016,9 @@
     <t xml:space="preserve">Orange / White</t>
   </si>
   <si>
+    <t xml:space="preserve">ASK SHIVA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Orange / Brown</t>
   </si>
   <si>
@@ -7040,10 +7046,16 @@
     <t xml:space="preserve">Mini Flat Maracas</t>
   </si>
   <si>
+    <t xml:space="preserve">INCLUDE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Natural Bamboo Xylophone with 5 Keys</t>
   </si>
   <si>
     <t xml:space="preserve">MI-XP-B-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMOVE</t>
   </si>
   <si>
     <t xml:space="preserve">Rectangle Wooden Maracas Shaker</t>
@@ -24064,42 +24076,45 @@
       <c r="A2" s="1" t="s">
         <v>2302</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>2303</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>390</v>
@@ -24107,7 +24122,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>387</v>
@@ -24115,7 +24130,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>393</v>
@@ -24123,7 +24138,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>396</v>
@@ -24131,289 +24146,316 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2328</v>
+        <v>2329</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>2330</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>349</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>347</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>2337</v>
+        <v>2339</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>2340</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>2339</v>
+        <v>2342</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>2343</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>2340</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>1245</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2342</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2346</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>1350</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2343</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2347</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>1347</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2344</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2348</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>2341</v>
+        <v>2345</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>1239</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>2345</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>2341</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>1233</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2346</v>
+        <v>2350</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>2340</v>
       </c>
     </row>
   </sheetData>
@@ -24462,245 +24504,284 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>2343</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>2347</v>
+        <v>2351</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2349</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>2347</v>
+        <v>2351</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1223</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>2350</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B4" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1265</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2352</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B5" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>447</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2353</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B6" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1270</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>2354</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B7" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1268</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>2355</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>2351</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>449</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>2356</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B9" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1272</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>2357</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B10" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1274</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B11" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>1276</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>2359</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B12" s="1" t="s">
-        <v>2351</v>
+        <v>2355</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1278</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>2360</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B13" s="1" t="s">
-        <v>2361</v>
+        <v>2365</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2362</v>
+        <v>2366</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>2363</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>2340</v>
+      </c>
       <c r="B14" s="1" t="s">
-        <v>2364</v>
+        <v>2368</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>264</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>2365</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>2343</v>
+      </c>
       <c r="B15" s="1" t="s">
-        <v>2366</v>
+        <v>2370</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>264</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2367</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1403</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>2369</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1401</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>2370</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1399</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>2371</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>1397</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>2372</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1395</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>2373</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>1393</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>2374</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>1391</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>2375</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>2368</v>
+        <v>2372</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>823</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>2376</v>
+        <v>2380</v>
       </c>
     </row>
   </sheetData>
